--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92577188148</v>
+        <v>46157.93188532841</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93188532841</v>
+        <v>46157.93408691617</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408691617</v>
+        <v>46157.93726407522</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93726407522</v>
+        <v>46158.28223902959</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223902959</v>
+        <v>46158.29716070705</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29716070705</v>
+        <v>46158.29824329317</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29824329317</v>
+        <v>46158.33394992462</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394992462</v>
+        <v>46158.36864704437</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864704437</v>
+        <v>46158.37295667875</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
